--- a/output/第10期計画_人口推計の基礎の検証.xlsx
+++ b/output/第10期計画_人口推計の基礎の検証.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>レッドチームNo.23</t>
+          <t>自己点検No.23</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
     <row r="23" ht="104" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>注1）本シートの結果により、レッドチームレビューNo.23の指摘（分子の差も確認する必要がある）が的中した。従来の説明は分母の差のみを要因としていたが、実際には分子の差の寄与の方が大きい。注2）分子と分母の寄与の合計（＋0.64＋0.46＝＋1.10）は実際の差（＋1.10）と一致しない。分子と分母を同時に置換する交互作用があるためである。分解は寄与の大小の比較に用い、按分には用いない。注3）第10期は見える化（国勢調査・社人研）に統一する方針としている。第9期計画の数値と一致しないことを第2章に明記する（別管理表 確認事項A22）。</t>
+          <t>注1）本シートの結果により、自己点検記録No.23の指摘（分子の差も確認する必要がある）のとおりであることが確認された。従来の説明は分母の差のみを要因としていたが、実際には分子の差の寄与の方が大きい。注2）分子と分母の寄与の合計（＋0.64＋0.46＝＋1.10）は実際の差（＋1.10）と一致しない。分子と分母を同時に置換する交互作用があるためである。分解は寄与の大小の比較に用い、按分には用いない。注3）第10期は見える化（国勢調査・社人研）に統一する方針としている。第9期計画の数値と一致しないことを第2章に明記する（別管理表 確認事項A22）。</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
     <row r="22" ht="104" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>注1）本シートは、基準人口の選択という「分析者の裁量」が結論を左右しないことを確認するものである。レッドチームレビューの記述ルールに従い、裁量の余地がある選択については感度を示す。注2）A4の2019年の値は、平成27年（2015年）と令和2年（2020年）の国勢調査の線形補間である。令和元年3月末の実測値ではない。感度の確認としては足りるが、基準人口として採用するには適さない。注3）階級別認定率（65〜74歳3.99％等）は、見える化B4系列からの逆算による（認定率の年齢調整分析）。逆算に丸め誤差を含む（主張A3の留保）。</t>
+          <t>注1）本シートは、基準人口の選択という「分析者の裁量」が結論を左右しないことを確認するものである。自己点検記録の記述ルールに従い、裁量の余地がある選択については感度を示す。注2）A4の2019年の値は、平成27年（2015年）と令和2年（2020年）の国勢調査の線形補間である。令和元年3月末の実測値ではない。感度の確認としては足りるが、基準人口として採用するには適さない。注3）階級別認定率（65〜74歳3.99％等）は、見える化B4系列からの逆算による（認定率の年齢調整分析）。逆算に丸め誤差を含む（主張A3の留保）。</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>新規。見える化A4。従来「令和9年度比で約27％増加」としていた値と整合する（令和9年2,212人→令和22年2,810人＝＋27.0％）。</t>
+          <t>新規。見える化A4。従来「令和9年度比で約27％増加」としていた値と符合する（令和9年2,212人→令和22年2,810人＝＋27.0％）。</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>撤回する。分子（高齢者数）の寄与＋0.64ポイントが分母（総人口）の寄与＋0.46ポイントを上回る。レッドチームレビューNo.23の指摘が的中した。</t>
+          <t>撤回する。分子（高齢者数）の寄与＋0.64ポイントが分母（総人口）の寄与＋0.46ポイントを上回る。自己点検記録No.23の指摘のとおりであることが確認された。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="22" ht="104" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>注1）A系列の受領により、新規の主張5件（A5〜A8）が加わり、1件（A9 分母の過大が原因）を撤回した。撤回はレッドチームレビューNo.23の指摘が的中したものである。注2）A系列は広域連合の合計値のみであり、町別の値を含まない。資料No.9（町別住民基本台帳人口）の必要性は変わらない。むしろ、広域計の基礎が固まったことで、町別の実績との突合が次の作業として明確になった。注3）人口推計の基礎が固まれば、認定率の設定（方針No.2）→見込量→給付費→保険料へと順に進めることができる。現在、仕様書４（5）将来推計の進捗は0.30であり、本表により基礎データの整理が完了した。</t>
+          <t>注1）A系列の受領により、新規の主張5件（A5〜A8）が加わり、1件（A9 分母の過大が原因）を撤回した。撤回は自己点検記録No.23の指摘のとおりであることが確認されたものである。注2）A系列は広域連合の合計値のみであり、町別の値を含まない。資料No.9（町別住民基本台帳人口）の必要性は変わらない。むしろ、広域計の基礎が固まったことで、町別の実績との突合が次の作業として明確になった。注3）人口推計の基礎が固まれば、認定率の設定（方針No.2）→見込量→給付費→保険料へと順に進めることができる。現在、仕様書４（5）将来推計の進捗は0.30であり、本表により基礎データの整理が完了した。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_人口推計の基礎の検証.xlsx
+++ b/output/第10期計画_人口推計の基礎の検証.xlsx
@@ -4621,7 +4621,7 @@
     <row r="23" ht="104" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>注1）本シートの結果により、自己点検記録No.23の指摘（分子の差も確認する必要がある）のとおりであることが確認された。従来の説明は分母の差のみを要因としていたが、実際には分子の差の寄与の方が大きい。注2）分子と分母の寄与の合計（＋0.64＋0.46＝＋1.10）は実際の差（＋1.10）と一致しない。分子と分母を同時に置換する交互作用があるためである。分解は寄与の大小の比較に用い、按分には用いない。注3）第10期は見える化（国勢調査・社人研）に統一する方針としている。第9期計画の数値と一致しないことを第2章に明記する（別管理表 確認事項A22）。</t>
+          <t>注1）本シートの結果により、受託者の自己点検による指摘（分子の差も確認する必要がある）のとおりであることが確認された。従来の説明は分母の差のみを要因としていたが、実際には分子の差の寄与の方が大きい。注2）分子と分母の寄与の合計（＋0.64＋0.46＝＋1.10）は実際の差（＋1.10）と一致しない。分子と分母を同時に置換する交互作用があるためである。分解は寄与の大小の比較に用い、按分には用いない。注3）第10期は見える化（国勢調査・社人研）に統一する方針としている。第9期計画の数値と一致しないことを第2章に明記する（別管理表 確認事項A22）。</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
     <row r="22" ht="104" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>注1）本シートは、基準人口の選択という「分析者の裁量」が結論を左右しないことを確認するものである。自己点検記録の記述ルールに従い、裁量の余地がある選択については感度を示す。注2）A4の2019年の値は、平成27年（2015年）と令和2年（2020年）の国勢調査の線形補間である。令和元年3月末の実測値ではない。感度の確認としては足りるが、基準人口として採用するには適さない。注3）階級別認定率（65〜74歳3.99％等）は、見える化B4系列からの逆算による（認定率の年齢調整分析）。逆算に丸め誤差を含む（主張A3の留保）。</t>
+          <t>注1）本シートは、基準人口の選択という「分析者の裁量」が結論を左右しないことを確認するものである。受託者の自己点検で定めた記述ルールに従い、裁量の余地がある選択については感度を示す。注2）A4の2019年の値は、平成27年（2015年）と令和2年（2020年）の国勢調査の線形補間である。令和元年3月末の実測値ではない。感度の確認としては足りるが、基準人口として採用するには適さない。注3）階級別認定率（65〜74歳3.99％等）は、見える化B4系列からの逆算による（認定率の年齢調整分析）。逆算に丸め誤差を含む（主張A3の留保）。</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5793,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「主張の根拠水準の棚卸しと再レビュー」の主張のうち、A系列により水準又は内容が変わるものを示す。</t>
+          <t>受託者の自己点検における主張のうち、A系列により水準又は内容が変わるものを示す。</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>撤回する。分子（高齢者数）の寄与＋0.64ポイントが分母（総人口）の寄与＋0.46ポイントを上回る。自己点検記録No.23の指摘のとおりであることが確認された。</t>
+          <t>撤回する。分子（高齢者数）の寄与＋0.64ポイントが分母（総人口）の寄与＋0.46ポイントを上回る。受託者の自己点検による指摘のとおりであることが確認された。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="22" ht="104" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>注1）A系列の受領により、新規の主張5件（A5〜A8）が加わり、1件（A9 分母の過大が原因）を撤回した。撤回は自己点検記録No.23の指摘のとおりであることが確認されたものである。注2）A系列は広域連合の合計値のみであり、町別の値を含まない。資料No.9（町別住民基本台帳人口）の必要性は変わらない。むしろ、広域計の基礎が固まったことで、町別の実績との突合が次の作業として明確になった。注3）人口推計の基礎が固まれば、認定率の設定（方針No.2）→見込量→給付費→保険料へと順に進めることができる。現在、仕様書４（5）将来推計の進捗は0.30であり、本表により基礎データの整理が完了した。</t>
+          <t>注1）A系列の受領により、新規の主張5件（A5〜A8）が加わり、1件（A9 分母の過大が原因）を撤回した。撤回は受託者の自己点検による指摘のとおりであることが確認されたものである。注2）A系列は広域連合の合計値のみであり、町別の値を含まない。資料No.9（町別住民基本台帳人口）の必要性は変わらない。むしろ、広域計の基礎が固まったことで、町別の実績との突合が次の作業として明確になった。注3）人口推計の基礎が固まれば、認定率の設定（方針No.2）→見込量→給付費→保険料へと順に進めることができる。現在、仕様書４（5）将来推計の進捗は0.30であり、本表により基礎データの整理が完了した。</t>
         </is>
       </c>
     </row>
